--- a/sample_output.xlsx
+++ b/sample_output.xlsx
@@ -19,7 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;¥&quot;#,##0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -34,7 +36,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -45,6 +47,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="004F46E5"/>
         <bgColor rgb="004F46E5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9FAFB"/>
+        <bgColor rgb="00F9FAFB"/>
       </patternFill>
     </fill>
   </fills>
@@ -60,11 +68,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -141,240 +154,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="11"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>商品別 売上合計（円）</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="bar"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'商品別集計'!D1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'商品別集計'!$A$2:$A$11</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'商品別集計'!$D$2:$D$11</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>売上合計</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>商品</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="12"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>日別 売上推移（円）</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'日別売上推移'!C1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'日別売上推移'!$A$2:$A$28</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'日別売上推移'!$C$2:$C$28</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>日付</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>売上合計</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -382,26 +163,59 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7920000" cy="4320000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
+    <ext cx="7048500" cy="3905250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
     <clientData/>
   </oneCellAnchor>
 </wsDr>
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="4953000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -409,19 +223,22 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="3600000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
+    <ext cx="8382000" cy="3619500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
     <clientData/>
   </oneCellAnchor>
 </wsDr>
@@ -719,15 +536,15 @@
   <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30.5" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="27.5" customWidth="1" min="3" max="3"/>
-    <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="24.84999999999999" customWidth="1" min="1" max="1"/>
+    <col width="14.5" customWidth="1" min="2" max="2"/>
+    <col width="38.2" customWidth="1" min="3" max="3"/>
+    <col width="7.4" customWidth="1" min="4" max="4"/>
+    <col width="7.6" customWidth="1" min="5" max="5"/>
+    <col width="20.6" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>注文番号</t>
@@ -760,28 +577,28 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>503-1827493-1029384</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>天然石ピアス（ローズクォーツ）</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="D2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="n">
         <v>2800</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
@@ -803,10 +620,10 @@
           <t>シルバーチェーンネックレス</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="6" t="n">
         <v>7000</v>
       </c>
       <c r="F3" t="inlineStr">
@@ -816,28 +633,28 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>503-1850274-1271093</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>レザーブレスレット</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="D4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>2400</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
@@ -859,10 +676,10 @@
           <t>バレッタ（大理石柄）</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="D5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="6" t="n">
         <v>1800</v>
       </c>
       <c r="F5" t="inlineStr">
@@ -872,28 +689,28 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>503-1875902-1523678</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>天然石ブレスレット（ターコイズ）</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
+      <c r="D6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>3200</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
@@ -915,10 +732,10 @@
           <t>天然石ピアス（アメジスト）</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="D7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="6" t="n">
         <v>2800</v>
       </c>
       <c r="F7" t="inlineStr">
@@ -928,28 +745,28 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>503-1901029-1798354</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>シルバーリング（シンプル）</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="D8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>2900</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
@@ -971,10 +788,10 @@
           <t>14kgf一粒淡水パールネックレス</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="6" t="n">
         <v>4200</v>
       </c>
       <c r="F9" t="inlineStr">
@@ -984,28 +801,28 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>503-1926158-2087911</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>ヘアクリップ（パール）</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="4" t="n">
         <v>3000</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
@@ -1027,10 +844,10 @@
           <t>天然石リング（ガーネット）</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="n">
+      <c r="D11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="6" t="n">
         <v>3800</v>
       </c>
       <c r="F11" t="inlineStr">
@@ -1040,28 +857,28 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>BASE-2026-00128</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>天然石ピアス（ローズクォーツ）</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
+      <c r="D12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4" t="n">
         <v>2800</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>自社BASE</t>
         </is>
@@ -1083,10 +900,10 @@
           <t>天然石ピアス（アメジスト）</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="n">
+      <c r="D13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="6" t="n">
         <v>2800</v>
       </c>
       <c r="F13" t="inlineStr">
@@ -1096,28 +913,28 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>BASE-2026-00130</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>シルバーチェーンネックレス</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="4" t="n">
         <v>7000</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>自社BASE</t>
         </is>
@@ -1139,10 +956,10 @@
           <t>バレッタ（大理石柄）</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" t="n">
+      <c r="D15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="6" t="n">
         <v>1800</v>
       </c>
       <c r="F15" t="inlineStr">
@@ -1152,28 +969,28 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>BASE-2026-00132</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>14kgf一粒淡水パールネックレス</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="n">
+      <c r="D16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>4200</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>自社BASE</t>
         </is>
@@ -1195,10 +1012,10 @@
           <t>レザーブレスレット</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="n">
+      <c r="D17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="6" t="n">
         <v>2400</v>
       </c>
       <c r="F17" t="inlineStr">
@@ -1208,28 +1025,28 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>BASE-2026-00134</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>天然石リング（ガーネット）</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" t="n">
+      <c r="D18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4" t="n">
         <v>3800</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>自社BASE</t>
         </is>
@@ -1251,10 +1068,10 @@
           <t>天然石ブレスレット（ターコイズ）</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="6" t="n">
         <v>6400</v>
       </c>
       <c r="F19" t="inlineStr">
@@ -1264,28 +1081,28 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>367-58293-2940381</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>天然石ピアス（ローズクォーツ）</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" t="n">
+      <c r="D20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="4" t="n">
         <v>2800</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>楽天市場</t>
         </is>
@@ -1307,10 +1124,10 @@
           <t>シルバーチェーンネックレス</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" t="n">
+      <c r="D21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="6" t="n">
         <v>3500</v>
       </c>
       <c r="F21" t="inlineStr">
@@ -1320,28 +1137,28 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>367-58502-3198811</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>天然石ピアス（アメジスト）</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="4" t="n">
         <v>5600</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>楽天市場</t>
         </is>
@@ -1363,10 +1180,10 @@
           <t>14kgf一粒淡水パールネックレス</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="n">
+      <c r="D23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="6" t="n">
         <v>4200</v>
       </c>
       <c r="F23" t="inlineStr">
@@ -1376,28 +1193,28 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>367-58729-3354091</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>レザーブレスレット</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" t="n">
+      <c r="D24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="4" t="n">
         <v>2400</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>楽天市場</t>
         </is>
@@ -1419,10 +1236,10 @@
           <t>天然石ピアス（ローズクォーツ）</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="n">
+      <c r="D25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="6" t="n">
         <v>2800</v>
       </c>
       <c r="F25" t="inlineStr">
@@ -1432,28 +1249,28 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>367-58960-3508914</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>2026-05-10</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>バレッタ（大理石柄）</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="4" t="n">
         <v>3600</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>楽天市場</t>
         </is>
@@ -1475,10 +1292,10 @@
           <t>シルバーリング（シンプル）</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" t="n">
+      <c r="D27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="6" t="n">
         <v>2900</v>
       </c>
       <c r="F27" t="inlineStr">
@@ -1488,28 +1305,28 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>367-59188-3699314</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>天然石ブレスレット（ターコイズ）</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" t="n">
+      <c r="D28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="4" t="n">
         <v>3200</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>楽天市場</t>
         </is>
@@ -1531,10 +1348,10 @@
           <t>ヘアクリップ（パール）</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="6" t="n">
         <v>4500</v>
       </c>
       <c r="F29" t="inlineStr">
@@ -1544,28 +1361,28 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>367-59417-3884516</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>天然石ピアス（アメジスト）</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" t="n">
+      <c r="D30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="4" t="n">
         <v>2800</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>楽天市場</t>
         </is>
@@ -1587,10 +1404,10 @@
           <t>14kgf一粒淡水パールネックレス</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" t="n">
+      <c r="D31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="6" t="n">
         <v>4200</v>
       </c>
       <c r="F31" t="inlineStr">
@@ -1600,28 +1417,28 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>367-59649-4063108</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>シルバーチェーンネックレス</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" t="n">
+      <c r="D32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="4" t="n">
         <v>3500</v>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>楽天市場</t>
         </is>
@@ -1643,10 +1460,10 @@
           <t>天然石リング（ガーネット）</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" t="n">
+      <c r="D33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="6" t="n">
         <v>3800</v>
       </c>
       <c r="F33" t="inlineStr">
@@ -1656,28 +1473,28 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>367-59882-4248893</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>天然石ピアス（ローズクォーツ）</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="4" t="n">
         <v>5600</v>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>楽天市場</t>
         </is>
@@ -1697,13 +1514,13 @@
   <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27.5" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="9.5" customWidth="1" min="4" max="4"/>
+    <col width="38.2" customWidth="1" min="1" max="1"/>
+    <col width="11.8" customWidth="1" min="2" max="2"/>
+    <col width="11.8" customWidth="1" min="3" max="3"/>
+    <col width="11.8" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>商品名</t>
@@ -1726,18 +1543,18 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>シルバーチェーンネックレス</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="4" t="n">
         <v>21000</v>
       </c>
     </row>
@@ -1747,29 +1564,29 @@
           <t>14kgf一粒淡水パールネックレス</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="6" t="n">
         <v>16800</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>天然石ピアス（ローズクォーツ）</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="4" t="n">
         <v>16800</v>
       </c>
     </row>
@@ -1779,29 +1596,29 @@
           <t>天然石ピアス（アメジスト）</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>14000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>天然石ブレスレット（ターコイズ）</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="4" t="n">
         <v>12800</v>
       </c>
     </row>
@@ -1811,29 +1628,29 @@
           <t>天然石リング（ガーネット）</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>11400</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>ヘアクリップ（パール）</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="4" t="n">
         <v>7500</v>
       </c>
     </row>
@@ -1843,29 +1660,29 @@
           <t>バレッタ（大理石柄）</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="6" t="n">
         <v>7200</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>レザーブレスレット</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="4" t="n">
         <v>7200</v>
       </c>
     </row>
@@ -1875,13 +1692,13 @@
           <t>シルバーリング（シンプル）</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="6" t="n">
         <v>5800</v>
       </c>
     </row>
@@ -1900,14 +1717,14 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="9.5" customWidth="1" min="4" max="4"/>
-    <col width="9.5" customWidth="1" min="5" max="5"/>
+    <col width="20.6" customWidth="1" min="1" max="1"/>
+    <col width="11.8" customWidth="1" min="2" max="2"/>
+    <col width="11.8" customWidth="1" min="3" max="3"/>
+    <col width="11.8" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>プラットフォーム</t>
@@ -1935,21 +1752,21 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>楽天市場</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="4" t="n">
         <v>55400</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>46.0%</t>
         </is>
@@ -1961,13 +1778,13 @@
           <t>Amazon</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="6" t="n">
         <v>33900</v>
       </c>
       <c r="E3" t="inlineStr">
@@ -1977,21 +1794,21 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>自社BASE</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="4" t="n">
         <v>31200</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>25.9%</t>
         </is>
@@ -1999,6 +1816,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2011,12 +1829,12 @@
   <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="9.5" customWidth="1" min="3" max="3"/>
+    <col width="14.5" customWidth="1" min="1" max="1"/>
+    <col width="11.8" customWidth="1" min="2" max="2"/>
+    <col width="11.8" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>注文日</t>
@@ -2034,15 +1852,15 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="n">
         <v>2800</v>
       </c>
     </row>
@@ -2052,23 +1870,23 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="6" t="n">
         <v>5600</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>3500</v>
       </c>
     </row>
@@ -2078,23 +1896,23 @@
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="6" t="n">
         <v>12600</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="4" t="n">
         <v>7000</v>
       </c>
     </row>
@@ -2104,23 +1922,23 @@
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
+      <c r="B7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="6" t="n">
         <v>2400</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
+      <c r="B8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>2400</v>
       </c>
     </row>
@@ -2130,23 +1948,23 @@
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="6" t="n">
         <v>8800</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="n">
+      <c r="B10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4" t="n">
         <v>2800</v>
       </c>
     </row>
@@ -2156,23 +1974,23 @@
           <t>2026-05-10</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="n">
+      <c r="B11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="6" t="n">
         <v>3600</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="4" t="n">
         <v>5000</v>
       </c>
     </row>
@@ -2182,23 +2000,23 @@
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="n">
+      <c r="B13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="6" t="n">
         <v>2900</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="n">
+      <c r="B14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4" t="n">
         <v>3200</v>
       </c>
     </row>
@@ -2208,23 +2026,23 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="n">
+      <c r="B15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="6" t="n">
         <v>2800</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="4" t="n">
         <v>8700</v>
       </c>
     </row>
@@ -2234,23 +2052,23 @@
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="n">
+      <c r="B17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="6" t="n">
         <v>2900</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="n">
+      <c r="B18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="4" t="n">
         <v>2800</v>
       </c>
     </row>
@@ -2260,23 +2078,23 @@
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="n">
+      <c r="B19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="6" t="n">
         <v>2400</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="n">
+      <c r="B20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="4" t="n">
         <v>4200</v>
       </c>
     </row>
@@ -2286,23 +2104,23 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="n">
+      <c r="B21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="6" t="n">
         <v>4200</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" t="n">
+      <c r="B22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="4" t="n">
         <v>3500</v>
       </c>
     </row>
@@ -2312,23 +2130,23 @@
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" t="n">
+      <c r="B23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="6" t="n">
         <v>3800</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" t="n">
+      <c r="B24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="4" t="n">
         <v>3000</v>
       </c>
     </row>
@@ -2338,23 +2156,23 @@
           <t>2026-05-24</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" t="n">
+      <c r="B25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="6" t="n">
         <v>3800</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" t="n">
+      <c r="B26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="4" t="n">
         <v>6400</v>
       </c>
     </row>
@@ -2364,23 +2182,23 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" t="n">
+      <c r="B27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="6" t="n">
         <v>3800</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" t="n">
+      <c r="B28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="4" t="n">
         <v>5600</v>
       </c>
     </row>
